--- a/CONTROL PROCESOS COCINA DULCE.xlsx
+++ b/CONTROL PROCESOS COCINA DULCE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariaalmenara-my.sharepoint.com/personal/lhora_mariaalmenara_pe/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergioruiz\Reportes\cocina_dulce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{01E7B672-4CD3-4345-8A56-4FEF72FA435A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB04EEA6-58C2-4115-B92B-79C179C5C9B2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127F221F-47CB-4729-B0DA-D6794B9EE0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A299860B-70D6-45FF-BB80-B67B2EAA8DCC}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>FUDGE</t>
   </si>
   <si>
-    <t>FUDGE SILVESTRE</t>
-  </si>
-  <si>
     <t>FUDGE LIQUIDO PARA TIENDA</t>
   </si>
   <si>
@@ -196,6 +193,9 @@
   </si>
   <si>
     <t>VELOCIDAD DEL AGITADOR (hz)/ BATIDORA/OTROS</t>
+  </si>
+  <si>
+    <t>FUDGE SUGAR FREE NUEVO</t>
   </si>
 </sst>
 </file>
@@ -423,13 +423,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -440,6 +437,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -452,6 +452,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -463,9 +466,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,9 +546,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -586,7 +586,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -692,7 +692,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -834,7 +834,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -860,7 +860,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -876,537 +876,537 @@
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="18"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="20"/>
-    </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="21"/>
+    </row>
+    <row r="4" spans="1:12" s="6" customFormat="1" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>44</v>
+      <c r="E5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>45</v>
+      <c r="E6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>49</v>
+      <c r="E7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="9"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="12" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="9"/>
+      <c r="E9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="8"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="9"/>
+      <c r="E10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
+      <c r="E11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
+      <c r="E12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="E13" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
-        <v>16</v>
+      <c r="A14" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
+      <c r="E14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
-        <v>17</v>
+      <c r="A15" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
+      <c r="E15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
-        <v>18</v>
+      <c r="A16" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
+      <c r="E16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
-        <v>19</v>
+      <c r="A17" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="E17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
-        <v>20</v>
+      <c r="A18" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="E18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
-        <v>21</v>
+      <c r="A19" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
+      <c r="E19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
-        <v>22</v>
+      <c r="A20" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
+      <c r="E20" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
-        <v>23</v>
+      <c r="A21" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
+      <c r="E21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
-        <v>24</v>
+      <c r="A22" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
+      <c r="E22" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
-        <v>25</v>
+      <c r="A23" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
+      <c r="E23" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
-        <v>50</v>
+      <c r="A24" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
+      <c r="E24" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A25" s="21" t="s">
-        <v>26</v>
+      <c r="A25" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
+      <c r="E25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
-        <v>27</v>
+      <c r="A26" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
+      <c r="E26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
-        <v>28</v>
+      <c r="A27" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
+      <c r="E27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
-        <v>29</v>
+      <c r="A28" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
+      <c r="E28" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
-        <v>30</v>
+      <c r="A29" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
+      <c r="E29" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>

--- a/CONTROL PROCESOS COCINA DULCE.xlsx
+++ b/CONTROL PROCESOS COCINA DULCE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergioruiz\Reportes\cocina_dulce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127F221F-47CB-4729-B0DA-D6794B9EE0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703005D4-7295-49FA-AD57-D401B8139203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A299860B-70D6-45FF-BB80-B67B2EAA8DCC}"/>
   </bookViews>
@@ -114,9 +114,6 @@
     <t>MANJAR LIQUIDO</t>
   </si>
   <si>
-    <t>MANJAR SILVESTRE</t>
-  </si>
-  <si>
     <t>CHOCOLATE RALLADO BITTER</t>
   </si>
   <si>
@@ -196,6 +193,9 @@
   </si>
   <si>
     <t>FUDGE SUGAR FREE NUEVO</t>
+  </si>
+  <si>
+    <t>MANJAR SUGAR FREE NUEVO</t>
   </si>
 </sst>
 </file>
@@ -860,7 +860,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="5" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -913,28 +913,28 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="K4" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="L4" s="11" t="s">
         <v>0</v>
@@ -948,7 +948,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -956,10 +956,10 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -978,10 +978,10 @@
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -1000,10 +1000,10 @@
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -1022,7 +1022,7 @@
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L8" s="8"/>
     </row>
@@ -1034,7 +1034,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -1042,7 +1042,7 @@
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L9" s="8"/>
     </row>
@@ -1062,7 +1062,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L10" s="8"/>
     </row>
@@ -1074,7 +1074,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -1092,7 +1092,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1200,7 +1200,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1320,13 +1320,13 @@
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -1338,13 +1338,13 @@
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
